--- a/site/docs/app-governance/method.xlsx
+++ b/site/docs/app-governance/method.xlsx
@@ -61,7 +61,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -163,10 +163,70 @@
     <row r="9">
       <c r="A9" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">Answer a publisher's audit letter, or test the audit response plan before one arrives: check proofs of purchase against installs and brief counsel</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">audit-response</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Buy new software or approve a purchase</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rationalization, with sam-toolkit/acquisition-gate-checklist.md (the gate runs first and sends an AI tool to ai-intake)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Check invoices before payment, or report what the practice saved</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rationalization, with sam-toolkit/invoice-verification.csv and sam-toolkit/savings-report.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Read contract terms or prepare for an upcoming renewal</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rationalization, with sam-toolkit/contract-terms-check.csv and sam-toolkit/renewal-calendar.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Check license entitlement against purchase records as a routine check</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">itam-maturity, with sam-toolkit/proof-of-purchase-check.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">Practice for CAMP, CSAM, CHAMP, AIGP, ITIL 4 Foundation, or the IAM Certificate</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr" s="0">
+      <c r="B14" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">cert-prep</t>
         </is>

--- a/site/docs/app-governance/method.xlsx
+++ b/site/docs/app-governance/method.xlsx
@@ -163,70 +163,82 @@
     <row r="9">
       <c r="A9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Answer a publisher's audit letter, or test the audit response plan before one arrives: check proofs of purchase against installs and brief counsel</t>
+          <t xml:space="preserve">Find installed software past or near end of life, with a CISA KEV needs-review flag, from a software inventory export: counts only, run on the person's own machine</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">audit-response</t>
+          <t xml:space="preserve">software-lifecycle</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Buy new software or approve a purchase</t>
+          <t xml:space="preserve">Answer a publisher's audit letter, or test the audit response plan before one arrives: check proofs of purchase against installs and brief counsel</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rationalization, with sam-toolkit/acquisition-gate-checklist.md (the gate runs first and sends an AI tool to ai-intake)</t>
+          <t xml:space="preserve">audit-response</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Check invoices before payment, or report what the practice saved</t>
+          <t xml:space="preserve">Buy new software or approve a purchase</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rationalization, with sam-toolkit/invoice-verification.csv and sam-toolkit/savings-report.csv</t>
+          <t xml:space="preserve">rationalization, with sam-toolkit/acquisition-gate-checklist.md (the gate runs first and sends an AI tool to ai-intake)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Read contract terms or prepare for an upcoming renewal</t>
+          <t xml:space="preserve">Check invoices before payment, or report what the practice saved</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rationalization, with sam-toolkit/contract-terms-check.csv and sam-toolkit/renewal-calendar.csv</t>
+          <t xml:space="preserve">rationalization, with sam-toolkit/invoice-verification.csv and sam-toolkit/savings-report.csv</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Check license entitlement against purchase records as a routine check</t>
+          <t xml:space="preserve">Read contract terms or prepare for an upcoming renewal</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">itam-maturity, with sam-toolkit/proof-of-purchase-check.csv</t>
+          <t xml:space="preserve">rationalization, with sam-toolkit/contract-terms-check.csv and sam-toolkit/renewal-calendar.csv</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">Check license entitlement against purchase records as a routine check</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">itam-maturity, with sam-toolkit/proof-of-purchase-check.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">Practice for CAMP, CSAM, CHAMP, AIGP, ITIL 4 Foundation, or the IAM Certificate</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr" s="0">
+      <c r="B15" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">cert-prep</t>
         </is>
